--- a/tests/metadata.xlsx
+++ b/tests/metadata.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\janek\Desktop\TESTY\tests\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\janek\Documents\GitHub\document_classificator\tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E491344-4153-4D21-9F2D-C6C3156F1D77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C579131-8144-4B90-A8C4-8910D2DA6062}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10755" yWindow="2985" windowWidth="23205" windowHeight="12210" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="metadata" sheetId="1" r:id="rId1"/>
@@ -4832,6 +4832,186 @@
     <t>2025-07-28T14:44:02.909920</t>
   </si>
   <si>
+    <t>bill_of_materials_190027.jpg</t>
+  </si>
+  <si>
+    <t>2025-07-28T16:22:00.868398</t>
+  </si>
+  <si>
+    <t>daily_report_1eba23.jpg</t>
+  </si>
+  <si>
+    <t>2025-07-28T16:22:06.516409</t>
+  </si>
+  <si>
+    <t>bill_of_materials_5edbe7.jpg</t>
+  </si>
+  <si>
+    <t>2025-07-28T16:22:13.208028</t>
+  </si>
+  <si>
+    <t>bill_of_materials_ff8b72.jpg</t>
+  </si>
+  <si>
+    <t>2025-07-28T16:22:22.600061</t>
+  </si>
+  <si>
+    <t>bill_of_materials_5f6b70.jpg</t>
+  </si>
+  <si>
+    <t>2025-07-28T16:22:29.093914</t>
+  </si>
+  <si>
+    <t>daily_report_a3a5df.jpg</t>
+  </si>
+  <si>
+    <t>2025-07-28T16:22:39.459839</t>
+  </si>
+  <si>
+    <t>daily_report_64a9a6.jpg</t>
+  </si>
+  <si>
+    <t>2025-07-28T16:22:46.049721</t>
+  </si>
+  <si>
+    <t>daily_report_924cc4.jpg</t>
+  </si>
+  <si>
+    <t>2025-07-28T16:22:53.966330</t>
+  </si>
+  <si>
+    <t>daily_report_48acae.jpg</t>
+  </si>
+  <si>
+    <t>2025-07-28T16:23:04.373990</t>
+  </si>
+  <si>
+    <t>maintenance_log_56da85.jpg</t>
+  </si>
+  <si>
+    <t>2025-07-28T16:23:14.401261</t>
+  </si>
+  <si>
+    <t>inspection_report_b162fd.jpg</t>
+  </si>
+  <si>
+    <t>2025-07-28T16:23:23.835464</t>
+  </si>
+  <si>
+    <t>bill_of_materials_86f3f3.jpg</t>
+  </si>
+  <si>
+    <t>2025-07-28T16:23:34.198024</t>
+  </si>
+  <si>
+    <t>inspection_report_349082.jpg</t>
+  </si>
+  <si>
+    <t>2025-07-28T16:23:41.151958</t>
+  </si>
+  <si>
+    <t>inspection_report_a876b9.jpg</t>
+  </si>
+  <si>
+    <t>2025-07-28T16:23:48.973939</t>
+  </si>
+  <si>
+    <t>inspection_report_adc833.jpg</t>
+  </si>
+  <si>
+    <t>2025-07-28T16:23:56.210487</t>
+  </si>
+  <si>
+    <t>maintenance_log_2fa1e1.jpg</t>
+  </si>
+  <si>
+    <t>2025-07-28T16:24:10.682870</t>
+  </si>
+  <si>
+    <t>maintenance_log_9ce2ad.jpg</t>
+  </si>
+  <si>
+    <t>2025-07-28T16:24:23.853631</t>
+  </si>
+  <si>
+    <t>maintenance_log_0dead3.jpg</t>
+  </si>
+  <si>
+    <t>2025-07-28T16:24:35.477818</t>
+  </si>
+  <si>
+    <t>maintenance_log_c2ef15.jpg</t>
+  </si>
+  <si>
+    <t>2025-07-28T16:24:44.242536</t>
+  </si>
+  <si>
+    <t>maintenance_log_8cfcf6.jpg</t>
+  </si>
+  <si>
+    <t>2025-07-28T16:24:54.707797</t>
+  </si>
+  <si>
+    <t>product_data_sheet_57bfcd.jpg</t>
+  </si>
+  <si>
+    <t>2025-07-28T16:25:02.649415</t>
+  </si>
+  <si>
+    <t>product_data_sheet_b630c0.jpg</t>
+  </si>
+  <si>
+    <t>2025-07-28T16:25:11.498686</t>
+  </si>
+  <si>
+    <t>product_data_sheet_383ba2.jpg</t>
+  </si>
+  <si>
+    <t>2025-07-28T16:25:19.438694</t>
+  </si>
+  <si>
+    <t>product_data_sheet_166ee3.jpg</t>
+  </si>
+  <si>
+    <t>2025-07-28T16:25:25.342761</t>
+  </si>
+  <si>
+    <t>product_data_sheet_f96034.jpg</t>
+  </si>
+  <si>
+    <t>2025-07-28T16:25:30.703133</t>
+  </si>
+  <si>
+    <t>quality_checklist_a6e173.jpg</t>
+  </si>
+  <si>
+    <t>2025-07-28T16:25:39.766736</t>
+  </si>
+  <si>
+    <t>quality_checklist_a2240d.jpg</t>
+  </si>
+  <si>
+    <t>2025-07-28T16:25:47.416937</t>
+  </si>
+  <si>
+    <t>product_data_sheet_042d97.jpg</t>
+  </si>
+  <si>
+    <t>2025-07-28T16:25:58.410894</t>
+  </si>
+  <si>
+    <t>quality_checklist_ed2456.jpg</t>
+  </si>
+  <si>
+    <t>2025-07-28T16:26:08.515288</t>
+  </si>
+  <si>
+    <t>product_data_sheet_6aef4b.jpg</t>
+  </si>
+  <si>
+    <t>2025-07-28T16:26:15.162182</t>
+  </si>
+  <si>
     <t>bill_of_materials_3559f3.jpg</t>
   </si>
   <si>
@@ -5010,186 +5190,6 @@
   </si>
   <si>
     <t>2025-07-28T16:19:53.269812</t>
-  </si>
-  <si>
-    <t>bill_of_materials_190027.jpg</t>
-  </si>
-  <si>
-    <t>2025-07-28T16:22:00.868398</t>
-  </si>
-  <si>
-    <t>daily_report_1eba23.jpg</t>
-  </si>
-  <si>
-    <t>2025-07-28T16:22:06.516409</t>
-  </si>
-  <si>
-    <t>bill_of_materials_5edbe7.jpg</t>
-  </si>
-  <si>
-    <t>2025-07-28T16:22:13.208028</t>
-  </si>
-  <si>
-    <t>bill_of_materials_ff8b72.jpg</t>
-  </si>
-  <si>
-    <t>2025-07-28T16:22:22.600061</t>
-  </si>
-  <si>
-    <t>bill_of_materials_5f6b70.jpg</t>
-  </si>
-  <si>
-    <t>2025-07-28T16:22:29.093914</t>
-  </si>
-  <si>
-    <t>daily_report_a3a5df.jpg</t>
-  </si>
-  <si>
-    <t>2025-07-28T16:22:39.459839</t>
-  </si>
-  <si>
-    <t>daily_report_64a9a6.jpg</t>
-  </si>
-  <si>
-    <t>2025-07-28T16:22:46.049721</t>
-  </si>
-  <si>
-    <t>daily_report_924cc4.jpg</t>
-  </si>
-  <si>
-    <t>2025-07-28T16:22:53.966330</t>
-  </si>
-  <si>
-    <t>daily_report_48acae.jpg</t>
-  </si>
-  <si>
-    <t>2025-07-28T16:23:04.373990</t>
-  </si>
-  <si>
-    <t>maintenance_log_56da85.jpg</t>
-  </si>
-  <si>
-    <t>2025-07-28T16:23:14.401261</t>
-  </si>
-  <si>
-    <t>inspection_report_b162fd.jpg</t>
-  </si>
-  <si>
-    <t>2025-07-28T16:23:23.835464</t>
-  </si>
-  <si>
-    <t>bill_of_materials_86f3f3.jpg</t>
-  </si>
-  <si>
-    <t>2025-07-28T16:23:34.198024</t>
-  </si>
-  <si>
-    <t>inspection_report_349082.jpg</t>
-  </si>
-  <si>
-    <t>2025-07-28T16:23:41.151958</t>
-  </si>
-  <si>
-    <t>inspection_report_a876b9.jpg</t>
-  </si>
-  <si>
-    <t>2025-07-28T16:23:48.973939</t>
-  </si>
-  <si>
-    <t>inspection_report_adc833.jpg</t>
-  </si>
-  <si>
-    <t>2025-07-28T16:23:56.210487</t>
-  </si>
-  <si>
-    <t>maintenance_log_2fa1e1.jpg</t>
-  </si>
-  <si>
-    <t>2025-07-28T16:24:10.682870</t>
-  </si>
-  <si>
-    <t>maintenance_log_9ce2ad.jpg</t>
-  </si>
-  <si>
-    <t>2025-07-28T16:24:23.853631</t>
-  </si>
-  <si>
-    <t>maintenance_log_0dead3.jpg</t>
-  </si>
-  <si>
-    <t>2025-07-28T16:24:35.477818</t>
-  </si>
-  <si>
-    <t>maintenance_log_c2ef15.jpg</t>
-  </si>
-  <si>
-    <t>2025-07-28T16:24:44.242536</t>
-  </si>
-  <si>
-    <t>maintenance_log_8cfcf6.jpg</t>
-  </si>
-  <si>
-    <t>2025-07-28T16:24:54.707797</t>
-  </si>
-  <si>
-    <t>product_data_sheet_57bfcd.jpg</t>
-  </si>
-  <si>
-    <t>2025-07-28T16:25:02.649415</t>
-  </si>
-  <si>
-    <t>product_data_sheet_b630c0.jpg</t>
-  </si>
-  <si>
-    <t>2025-07-28T16:25:11.498686</t>
-  </si>
-  <si>
-    <t>product_data_sheet_383ba2.jpg</t>
-  </si>
-  <si>
-    <t>2025-07-28T16:25:19.438694</t>
-  </si>
-  <si>
-    <t>product_data_sheet_166ee3.jpg</t>
-  </si>
-  <si>
-    <t>2025-07-28T16:25:25.342761</t>
-  </si>
-  <si>
-    <t>product_data_sheet_f96034.jpg</t>
-  </si>
-  <si>
-    <t>2025-07-28T16:25:30.703133</t>
-  </si>
-  <si>
-    <t>quality_checklist_a6e173.jpg</t>
-  </si>
-  <si>
-    <t>2025-07-28T16:25:39.766736</t>
-  </si>
-  <si>
-    <t>quality_checklist_a2240d.jpg</t>
-  </si>
-  <si>
-    <t>2025-07-28T16:25:47.416937</t>
-  </si>
-  <si>
-    <t>product_data_sheet_042d97.jpg</t>
-  </si>
-  <si>
-    <t>2025-07-28T16:25:58.410894</t>
-  </si>
-  <si>
-    <t>quality_checklist_ed2456.jpg</t>
-  </si>
-  <si>
-    <t>2025-07-28T16:26:08.515288</t>
-  </si>
-  <si>
-    <t>product_data_sheet_6aef4b.jpg</t>
-  </si>
-  <si>
-    <t>2025-07-28T16:26:15.162182</t>
   </si>
 </sst>
 </file>
@@ -27999,10 +27999,10 @@
         <v>631</v>
       </c>
       <c r="G791" s="15" t="s">
-        <v>1659</v>
+        <v>1599</v>
       </c>
       <c r="H791" s="15" t="s">
-        <v>1660</v>
+        <v>1600</v>
       </c>
       <c r="I791" s="15">
         <v>6.52</v>
@@ -28028,10 +28028,10 @@
         <v>642</v>
       </c>
       <c r="G792" t="s">
-        <v>1661</v>
+        <v>1601</v>
       </c>
       <c r="H792" t="s">
-        <v>1662</v>
+        <v>1602</v>
       </c>
       <c r="I792">
         <v>5.5389999999999997</v>
@@ -28057,10 +28057,10 @@
         <v>631</v>
       </c>
       <c r="G793" s="15" t="s">
-        <v>1663</v>
+        <v>1603</v>
       </c>
       <c r="H793" s="15" t="s">
-        <v>1664</v>
+        <v>1604</v>
       </c>
       <c r="I793" s="15">
         <v>6.556</v>
@@ -28086,10 +28086,10 @@
         <v>631</v>
       </c>
       <c r="G794" s="15" t="s">
-        <v>1665</v>
+        <v>1605</v>
       </c>
       <c r="H794" s="15" t="s">
-        <v>1666</v>
+        <v>1606</v>
       </c>
       <c r="I794" s="15">
         <v>9.2590000000000003</v>
@@ -28115,10 +28115,10 @@
         <v>631</v>
       </c>
       <c r="G795" s="15" t="s">
-        <v>1667</v>
+        <v>1607</v>
       </c>
       <c r="H795" s="15" t="s">
-        <v>1668</v>
+        <v>1608</v>
       </c>
       <c r="I795" s="15">
         <v>6.3579999999999997</v>
@@ -28144,10 +28144,10 @@
         <v>642</v>
       </c>
       <c r="G796" s="15" t="s">
-        <v>1669</v>
+        <v>1609</v>
       </c>
       <c r="H796" s="15" t="s">
-        <v>1670</v>
+        <v>1610</v>
       </c>
       <c r="I796" s="15">
         <v>10.23</v>
@@ -28173,10 +28173,10 @@
         <v>642</v>
       </c>
       <c r="G797" s="15" t="s">
-        <v>1671</v>
+        <v>1611</v>
       </c>
       <c r="H797" s="15" t="s">
-        <v>1672</v>
+        <v>1612</v>
       </c>
       <c r="I797" s="15">
         <v>6.4509999999999996</v>
@@ -28202,10 +28202,10 @@
         <v>642</v>
       </c>
       <c r="G798" s="15" t="s">
-        <v>1673</v>
+        <v>1613</v>
       </c>
       <c r="H798" s="15" t="s">
-        <v>1674</v>
+        <v>1614</v>
       </c>
       <c r="I798" s="15">
         <v>6.407</v>
@@ -28231,10 +28231,10 @@
         <v>642</v>
       </c>
       <c r="G799" s="15" t="s">
-        <v>1675</v>
+        <v>1615</v>
       </c>
       <c r="H799" s="15" t="s">
-        <v>1676</v>
+        <v>1616</v>
       </c>
       <c r="I799" s="15">
         <v>10.273</v>
@@ -28260,10 +28260,10 @@
         <v>664</v>
       </c>
       <c r="G800" t="s">
-        <v>1677</v>
+        <v>1617</v>
       </c>
       <c r="H800" t="s">
-        <v>1678</v>
+        <v>1618</v>
       </c>
       <c r="I800">
         <v>9.8989999999999991</v>
@@ -28289,10 +28289,10 @@
         <v>653</v>
       </c>
       <c r="G801" s="15" t="s">
-        <v>1679</v>
+        <v>1619</v>
       </c>
       <c r="H801" s="15" t="s">
-        <v>1680</v>
+        <v>1620</v>
       </c>
       <c r="I801" s="15">
         <v>9.298</v>
@@ -28318,10 +28318,10 @@
         <v>631</v>
       </c>
       <c r="G802" t="s">
-        <v>1681</v>
+        <v>1621</v>
       </c>
       <c r="H802" t="s">
-        <v>1682</v>
+        <v>1622</v>
       </c>
       <c r="I802">
         <v>10.224</v>
@@ -28347,10 +28347,10 @@
         <v>653</v>
       </c>
       <c r="G803" s="15" t="s">
-        <v>1683</v>
+        <v>1623</v>
       </c>
       <c r="H803" s="15" t="s">
-        <v>1684</v>
+        <v>1624</v>
       </c>
       <c r="I803" s="15">
         <v>5.8159999999999998</v>
@@ -28376,10 +28376,10 @@
         <v>653</v>
       </c>
       <c r="G804" s="15" t="s">
-        <v>1685</v>
+        <v>1625</v>
       </c>
       <c r="H804" s="15" t="s">
-        <v>1686</v>
+        <v>1626</v>
       </c>
       <c r="I804" s="15">
         <v>7.6870000000000003</v>
@@ -28405,10 +28405,10 @@
         <v>653</v>
       </c>
       <c r="G805" s="15" t="s">
-        <v>1687</v>
+        <v>1627</v>
       </c>
       <c r="H805" s="15" t="s">
-        <v>1688</v>
+        <v>1628</v>
       </c>
       <c r="I805" s="15">
         <v>7.0940000000000003</v>
@@ -28434,10 +28434,10 @@
         <v>664</v>
       </c>
       <c r="G806" s="15" t="s">
-        <v>1689</v>
+        <v>1629</v>
       </c>
       <c r="H806" s="15" t="s">
-        <v>1690</v>
+        <v>1630</v>
       </c>
       <c r="I806" s="15">
         <v>14.343999999999999</v>
@@ -28463,10 +28463,10 @@
         <v>664</v>
       </c>
       <c r="G807" s="15" t="s">
-        <v>1691</v>
+        <v>1631</v>
       </c>
       <c r="H807" s="15" t="s">
-        <v>1692</v>
+        <v>1632</v>
       </c>
       <c r="I807" s="15">
         <v>12.712999999999999</v>
@@ -28492,10 +28492,10 @@
         <v>664</v>
       </c>
       <c r="G808" s="15" t="s">
-        <v>1693</v>
+        <v>1633</v>
       </c>
       <c r="H808" s="15" t="s">
-        <v>1694</v>
+        <v>1634</v>
       </c>
       <c r="I808" s="15">
         <v>11.46</v>
@@ -28521,10 +28521,10 @@
         <v>664</v>
       </c>
       <c r="G809" s="15" t="s">
-        <v>1695</v>
+        <v>1635</v>
       </c>
       <c r="H809" s="15" t="s">
-        <v>1696</v>
+        <v>1636</v>
       </c>
       <c r="I809" s="15">
         <v>8.6300000000000008</v>
@@ -28550,10 +28550,10 @@
         <v>664</v>
       </c>
       <c r="G810" s="15" t="s">
-        <v>1697</v>
+        <v>1637</v>
       </c>
       <c r="H810" s="15" t="s">
-        <v>1698</v>
+        <v>1638</v>
       </c>
       <c r="I810" s="15">
         <v>10.324</v>
@@ -28579,10 +28579,10 @@
         <v>675</v>
       </c>
       <c r="G811" s="15" t="s">
-        <v>1699</v>
+        <v>1639</v>
       </c>
       <c r="H811" s="15" t="s">
-        <v>1700</v>
+        <v>1640</v>
       </c>
       <c r="I811" s="15">
         <v>7.8049999999999997</v>
@@ -28608,10 +28608,10 @@
         <v>675</v>
       </c>
       <c r="G812" s="15" t="s">
-        <v>1701</v>
+        <v>1641</v>
       </c>
       <c r="H812" s="15" t="s">
-        <v>1702</v>
+        <v>1642</v>
       </c>
       <c r="I812" s="15">
         <v>8.6790000000000003</v>
@@ -28637,10 +28637,10 @@
         <v>675</v>
       </c>
       <c r="G813" s="15" t="s">
-        <v>1703</v>
+        <v>1643</v>
       </c>
       <c r="H813" s="15" t="s">
-        <v>1704</v>
+        <v>1644</v>
       </c>
       <c r="I813" s="15">
         <v>7.7969999999999997</v>
@@ -28666,10 +28666,10 @@
         <v>675</v>
       </c>
       <c r="G814" s="15" t="s">
-        <v>1705</v>
+        <v>1645</v>
       </c>
       <c r="H814" s="15" t="s">
-        <v>1706</v>
+        <v>1646</v>
       </c>
       <c r="I814" s="15">
         <v>5.7759999999999998</v>
@@ -28695,10 +28695,10 @@
         <v>675</v>
       </c>
       <c r="G815" s="15" t="s">
-        <v>1707</v>
+        <v>1647</v>
       </c>
       <c r="H815" s="15" t="s">
-        <v>1708</v>
+        <v>1648</v>
       </c>
       <c r="I815" s="15">
         <v>5.194</v>
@@ -28724,10 +28724,10 @@
         <v>686</v>
       </c>
       <c r="G816" s="15" t="s">
-        <v>1709</v>
+        <v>1649</v>
       </c>
       <c r="H816" s="15" t="s">
-        <v>1710</v>
+        <v>1650</v>
       </c>
       <c r="I816" s="15">
         <v>8.9350000000000005</v>
@@ -28753,10 +28753,10 @@
         <v>686</v>
       </c>
       <c r="G817" s="15" t="s">
-        <v>1711</v>
+        <v>1651</v>
       </c>
       <c r="H817" s="15" t="s">
-        <v>1712</v>
+        <v>1652</v>
       </c>
       <c r="I817" s="15">
         <v>7.3140000000000001</v>
@@ -28782,10 +28782,10 @@
         <v>675</v>
       </c>
       <c r="G818" t="s">
-        <v>1713</v>
+        <v>1653</v>
       </c>
       <c r="H818" t="s">
-        <v>1714</v>
+        <v>1654</v>
       </c>
       <c r="I818">
         <v>10.848000000000001</v>
@@ -28811,10 +28811,10 @@
         <v>686</v>
       </c>
       <c r="G819" s="15" t="s">
-        <v>1715</v>
+        <v>1655</v>
       </c>
       <c r="H819" s="15" t="s">
-        <v>1716</v>
+        <v>1656</v>
       </c>
       <c r="I819" s="15">
         <v>9.8640000000000008</v>
@@ -28840,10 +28840,10 @@
         <v>675</v>
       </c>
       <c r="G820" t="s">
-        <v>1717</v>
+        <v>1657</v>
       </c>
       <c r="H820" t="s">
-        <v>1718</v>
+        <v>1658</v>
       </c>
       <c r="I820">
         <v>6.5090000000000003</v>
@@ -28882,10 +28882,10 @@
         <v>631</v>
       </c>
       <c r="G822" s="14" t="s">
-        <v>1599</v>
+        <v>1659</v>
       </c>
       <c r="H822" s="14" t="s">
-        <v>1600</v>
+        <v>1660</v>
       </c>
       <c r="I822" s="14">
         <v>6.15</v>
@@ -28911,10 +28911,10 @@
         <v>631</v>
       </c>
       <c r="G823" s="14" t="s">
-        <v>1601</v>
+        <v>1661</v>
       </c>
       <c r="H823" s="14" t="s">
-        <v>1602</v>
+        <v>1662</v>
       </c>
       <c r="I823" s="14">
         <v>6.8289999999999997</v>
@@ -28940,10 +28940,10 @@
         <v>631</v>
       </c>
       <c r="G824" s="14" t="s">
-        <v>1603</v>
+        <v>1663</v>
       </c>
       <c r="H824" s="14" t="s">
-        <v>1604</v>
+        <v>1664</v>
       </c>
       <c r="I824" s="14">
         <v>6.7169999999999996</v>
@@ -28969,10 +28969,10 @@
         <v>642</v>
       </c>
       <c r="G825" t="s">
-        <v>1605</v>
+        <v>1665</v>
       </c>
       <c r="H825" t="s">
-        <v>1606</v>
+        <v>1666</v>
       </c>
       <c r="I825">
         <v>3.3809999999999998</v>
@@ -28998,10 +28998,10 @@
         <v>631</v>
       </c>
       <c r="G826" s="14" t="s">
-        <v>1607</v>
+        <v>1667</v>
       </c>
       <c r="H826" s="14" t="s">
-        <v>1608</v>
+        <v>1668</v>
       </c>
       <c r="I826" s="14">
         <v>9.8610000000000007</v>
@@ -29027,10 +29027,10 @@
         <v>642</v>
       </c>
       <c r="G827" s="14" t="s">
-        <v>1609</v>
+        <v>1669</v>
       </c>
       <c r="H827" s="14" t="s">
-        <v>1610</v>
+        <v>1670</v>
       </c>
       <c r="I827" s="14">
         <v>8.9570000000000007</v>
@@ -29056,10 +29056,10 @@
         <v>642</v>
       </c>
       <c r="G828" s="14" t="s">
-        <v>1611</v>
+        <v>1671</v>
       </c>
       <c r="H828" s="14" t="s">
-        <v>1612</v>
+        <v>1672</v>
       </c>
       <c r="I828" s="14">
         <v>8.5340000000000007</v>
@@ -29085,10 +29085,10 @@
         <v>771</v>
       </c>
       <c r="G829" t="s">
-        <v>1613</v>
+        <v>1673</v>
       </c>
       <c r="H829" t="s">
-        <v>1614</v>
+        <v>1674</v>
       </c>
       <c r="I829">
         <v>3.5249999999999999</v>
@@ -29114,10 +29114,10 @@
         <v>771</v>
       </c>
       <c r="G830" t="s">
-        <v>1615</v>
+        <v>1675</v>
       </c>
       <c r="H830" t="s">
-        <v>1616</v>
+        <v>1676</v>
       </c>
       <c r="I830">
         <v>3.5070000000000001</v>
@@ -29143,10 +29143,10 @@
         <v>631</v>
       </c>
       <c r="G831" t="s">
-        <v>1617</v>
+        <v>1677</v>
       </c>
       <c r="H831" t="s">
-        <v>1618</v>
+        <v>1678</v>
       </c>
       <c r="I831">
         <v>8.968</v>
@@ -29172,10 +29172,10 @@
         <v>631</v>
       </c>
       <c r="G832" t="s">
-        <v>1619</v>
+        <v>1679</v>
       </c>
       <c r="H832" t="s">
-        <v>1620</v>
+        <v>1680</v>
       </c>
       <c r="I832">
         <v>9.9109999999999996</v>
@@ -29201,10 +29201,10 @@
         <v>653</v>
       </c>
       <c r="G833" s="14" t="s">
-        <v>1621</v>
+        <v>1681</v>
       </c>
       <c r="H833" s="14" t="s">
-        <v>1622</v>
+        <v>1682</v>
       </c>
       <c r="I833" s="14">
         <v>4.2519999999999998</v>
@@ -29230,10 +29230,10 @@
         <v>642</v>
       </c>
       <c r="G834" t="s">
-        <v>1623</v>
+        <v>1683</v>
       </c>
       <c r="H834" t="s">
-        <v>1624</v>
+        <v>1684</v>
       </c>
       <c r="I834">
         <v>3.5539999999999998</v>
@@ -29259,10 +29259,10 @@
         <v>653</v>
       </c>
       <c r="G835" s="14" t="s">
-        <v>1625</v>
+        <v>1685</v>
       </c>
       <c r="H835" s="14" t="s">
-        <v>1626</v>
+        <v>1686</v>
       </c>
       <c r="I835" s="14">
         <v>6.46</v>
@@ -29288,10 +29288,10 @@
         <v>631</v>
       </c>
       <c r="G836" t="s">
-        <v>1627</v>
+        <v>1687</v>
       </c>
       <c r="H836" t="s">
-        <v>1628</v>
+        <v>1688</v>
       </c>
       <c r="I836">
         <v>9.2140000000000004</v>
@@ -29317,10 +29317,10 @@
         <v>771</v>
       </c>
       <c r="G837" t="s">
-        <v>1629</v>
+        <v>1689</v>
       </c>
       <c r="H837" t="s">
-        <v>1630</v>
+        <v>1690</v>
       </c>
       <c r="I837">
         <v>3.778</v>
@@ -29346,10 +29346,10 @@
         <v>771</v>
       </c>
       <c r="G838" t="s">
-        <v>1631</v>
+        <v>1691</v>
       </c>
       <c r="H838" t="s">
-        <v>1632</v>
+        <v>1692</v>
       </c>
       <c r="I838">
         <v>3.4350000000000001</v>
@@ -29375,10 +29375,10 @@
         <v>771</v>
       </c>
       <c r="G839" t="s">
-        <v>1633</v>
+        <v>1693</v>
       </c>
       <c r="H839" t="s">
-        <v>1634</v>
+        <v>1694</v>
       </c>
       <c r="I839">
         <v>3.3769999999999998</v>
@@ -29404,10 +29404,10 @@
         <v>664</v>
       </c>
       <c r="G840" s="14" t="s">
-        <v>1635</v>
+        <v>1695</v>
       </c>
       <c r="H840" s="14" t="s">
-        <v>1636</v>
+        <v>1696</v>
       </c>
       <c r="I840" s="14">
         <v>7.1630000000000003</v>
@@ -29433,10 +29433,10 @@
         <v>771</v>
       </c>
       <c r="G841" t="s">
-        <v>1637</v>
+        <v>1697</v>
       </c>
       <c r="H841" t="s">
-        <v>1638</v>
+        <v>1698</v>
       </c>
       <c r="I841">
         <v>3.399</v>
@@ -29462,10 +29462,10 @@
         <v>675</v>
       </c>
       <c r="G842" s="14" t="s">
-        <v>1639</v>
+        <v>1699</v>
       </c>
       <c r="H842" s="14" t="s">
-        <v>1640</v>
+        <v>1700</v>
       </c>
       <c r="I842" s="14">
         <v>6.2750000000000004</v>
@@ -29491,10 +29491,10 @@
         <v>771</v>
       </c>
       <c r="G843" t="s">
-        <v>1641</v>
+        <v>1701</v>
       </c>
       <c r="H843" t="s">
-        <v>1642</v>
+        <v>1702</v>
       </c>
       <c r="I843">
         <v>3.4529999999999998</v>
@@ -29520,10 +29520,10 @@
         <v>771</v>
       </c>
       <c r="G844" t="s">
-        <v>1643</v>
+        <v>1703</v>
       </c>
       <c r="H844" t="s">
-        <v>1644</v>
+        <v>1704</v>
       </c>
       <c r="I844">
         <v>3.6440000000000001</v>
@@ -29549,10 +29549,10 @@
         <v>675</v>
       </c>
       <c r="G845" s="14" t="s">
-        <v>1645</v>
+        <v>1705</v>
       </c>
       <c r="H845" s="14" t="s">
-        <v>1646</v>
+        <v>1706</v>
       </c>
       <c r="I845" s="14">
         <v>9.4550000000000001</v>
@@ -29578,10 +29578,10 @@
         <v>675</v>
       </c>
       <c r="G846" s="14" t="s">
-        <v>1647</v>
+        <v>1707</v>
       </c>
       <c r="H846" s="14" t="s">
-        <v>1648</v>
+        <v>1708</v>
       </c>
       <c r="I846" s="14">
         <v>6.859</v>
@@ -29607,10 +29607,10 @@
         <v>771</v>
       </c>
       <c r="G847" t="s">
-        <v>1649</v>
+        <v>1709</v>
       </c>
       <c r="H847" t="s">
-        <v>1650</v>
+        <v>1710</v>
       </c>
       <c r="I847">
         <v>3.1840000000000002</v>
@@ -29636,10 +29636,10 @@
         <v>771</v>
       </c>
       <c r="G848" t="s">
-        <v>1651</v>
+        <v>1711</v>
       </c>
       <c r="H848" t="s">
-        <v>1652</v>
+        <v>1712</v>
       </c>
       <c r="I848">
         <v>3.274</v>
@@ -29665,10 +29665,10 @@
         <v>771</v>
       </c>
       <c r="G849" t="s">
-        <v>1653</v>
+        <v>1713</v>
       </c>
       <c r="H849" t="s">
-        <v>1654</v>
+        <v>1714</v>
       </c>
       <c r="I849">
         <v>3.698</v>
@@ -29694,10 +29694,10 @@
         <v>771</v>
       </c>
       <c r="G850" t="s">
-        <v>1655</v>
+        <v>1715</v>
       </c>
       <c r="H850" t="s">
-        <v>1656</v>
+        <v>1716</v>
       </c>
       <c r="I850">
         <v>3.42</v>
@@ -29723,10 +29723,10 @@
         <v>686</v>
       </c>
       <c r="G851" s="14" t="s">
-        <v>1657</v>
+        <v>1717</v>
       </c>
       <c r="H851" s="14" t="s">
-        <v>1658</v>
+        <v>1718</v>
       </c>
       <c r="I851" s="14">
         <v>7.6130000000000004</v>
